--- a/2025/IDL/Tps/Tp1/Tp1.xlsx
+++ b/2025/IDL/Tps/Tp1/Tp1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin\Documents\GitHub\Ing-Computacion\3er Año\IDL\Tps\Tp1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin\Documents\GitHub\Ing-Computacion\2025\IDL\Tps\Tp1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC93C39-DB92-4ECA-8667-0A806B81398A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BEFDF95-D39F-46E3-987E-41DCF149E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D373F859-B24E-4A05-9B94-9250138E0FA3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="56">
   <si>
     <t>S0</t>
   </si>
@@ -726,16 +726,16 @@
         <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="U1" s="3" t="s">
         <v>38</v>

--- a/2025/IDL/Tps/Tp1/Tp1.xlsx
+++ b/2025/IDL/Tps/Tp1/Tp1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquin\Documents\GitHub\Ing-Computacion\2025\IDL\Tps\Tp1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BEFDF95-D39F-46E3-987E-41DCF149E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC179827-F4D4-4B0F-BB86-D920EDFAE8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D373F859-B24E-4A05-9B94-9250138E0FA3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D373F859-B24E-4A05-9B94-9250138E0FA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Punto2" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="59">
   <si>
     <t>S0</t>
   </si>
@@ -204,6 +204,15 @@
   </si>
   <si>
     <t>Segmentos del display 2</t>
+  </si>
+  <si>
+    <t>Punto DP</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
@@ -290,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -321,6 +330,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -668,15 +680,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCDE0545-F1EC-45EE-8F53-AA277A81BD0D}">
-  <dimension ref="A1:AP26"/>
+  <dimension ref="A1:AR27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="28" max="28" width="10" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -738,54 +751,60 @@
         <v>20</v>
       </c>
       <c r="U1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
@@ -832,77 +851,83 @@
       <c r="P2" s="4">
         <v>1</v>
       </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="5">
-        <v>0</v>
-      </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
-      <c r="U2" s="6">
-        <v>1</v>
-      </c>
-      <c r="V2" s="6">
-        <v>1</v>
+      <c r="Q2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="W2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" s="6">
         <v>0</v>
       </c>
-      <c r="AB2" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="7">
-        <v>1</v>
+      <c r="AB2" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="6">
+        <v>0</v>
       </c>
       <c r="AD2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="7">
         <v>0</v>
       </c>
-      <c r="AI2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
+      <c r="AI2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="AL2" s="2"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
       <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>16</v>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>0</v>
       </c>
       <c r="B3" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="4">
         <v>1</v>
@@ -956,13 +981,13 @@
         <v>0</v>
       </c>
       <c r="T3" s="5">
-        <v>1</v>
-      </c>
-      <c r="U3" s="6">
-        <v>1</v>
-      </c>
-      <c r="V3" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>1</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="W3" s="6">
         <v>1</v>
@@ -977,49 +1002,55 @@
         <v>1</v>
       </c>
       <c r="AA3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AB3" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="6">
+        <v>0</v>
       </c>
       <c r="AD3" s="7">
         <v>1</v>
       </c>
       <c r="AE3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH3" s="7">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="AI3" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="2"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>16</v>
+      <c r="B4" s="4">
+        <v>0</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1067,16 +1098,16 @@
         <v>0</v>
       </c>
       <c r="S4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" s="5">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6">
-        <v>1</v>
-      </c>
-      <c r="V4" s="6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U4" s="5">
+        <v>1</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="W4" s="6">
         <v>1</v>
@@ -1091,13 +1122,13 @@
         <v>1</v>
       </c>
       <c r="AA4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="6">
+        <v>0</v>
       </c>
       <c r="AD4" s="7">
         <v>0</v>
@@ -1112,31 +1143,37 @@
         <v>0</v>
       </c>
       <c r="AH4" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="AL4" s="2"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
       <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
+      <c r="C5" s="4">
+        <v>0</v>
       </c>
       <c r="D5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4">
         <v>1</v>
@@ -1184,13 +1221,13 @@
         <v>1</v>
       </c>
       <c r="T5" s="5">
-        <v>1</v>
-      </c>
-      <c r="U5" s="6">
-        <v>1</v>
-      </c>
-      <c r="V5" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>1</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="W5" s="6">
         <v>1</v>
@@ -1205,13 +1242,13 @@
         <v>1</v>
       </c>
       <c r="AA5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="6">
+        <v>0</v>
       </c>
       <c r="AD5" s="7">
         <v>1</v>
@@ -1223,23 +1260,29 @@
         <v>0</v>
       </c>
       <c r="AG5" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="7">
         <v>1</v>
       </c>
-      <c r="AI5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="2"/>
+      <c r="AI5" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
       <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="2"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>16</v>
       </c>
@@ -1249,11 +1292,11 @@
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>16</v>
+      <c r="D6" s="4">
+        <v>0</v>
       </c>
       <c r="E6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -1292,19 +1335,19 @@
         <v>0</v>
       </c>
       <c r="R6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="5">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6">
-        <v>1</v>
-      </c>
-      <c r="V6" s="6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U6" s="5">
+        <v>1</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="W6" s="6">
         <v>1</v>
@@ -1319,41 +1362,47 @@
         <v>1</v>
       </c>
       <c r="AA6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="6">
+        <v>0</v>
       </c>
       <c r="AD6" s="7">
         <v>1</v>
       </c>
       <c r="AE6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" s="7">
         <v>1</v>
       </c>
       <c r="AH6" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
       <c r="AO6" s="2"/>
       <c r="AP6" s="2"/>
+      <c r="AQ6" s="2"/>
+      <c r="AR6" s="2"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -1366,11 +1415,11 @@
       <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>16</v>
+      <c r="E7" s="4">
+        <v>0</v>
       </c>
       <c r="F7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4">
         <v>1</v>
@@ -1412,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="T7" s="5">
-        <v>1</v>
-      </c>
-      <c r="U7" s="6">
-        <v>1</v>
-      </c>
-      <c r="V7" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>1</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="W7" s="6">
         <v>1</v>
@@ -1433,41 +1482,47 @@
         <v>1</v>
       </c>
       <c r="AA7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="6">
         <v>0</v>
       </c>
       <c r="AD7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="7">
         <v>1</v>
       </c>
       <c r="AF7" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ7" s="2"/>
-      <c r="AK7" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK7" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="AL7" s="2"/>
       <c r="AM7" s="2"/>
       <c r="AN7" s="2"/>
       <c r="AO7" s="2"/>
       <c r="AP7" s="2"/>
+      <c r="AQ7" s="2"/>
+      <c r="AR7" s="2"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -1483,11 +1538,11 @@
       <c r="E8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>16</v>
+      <c r="F8" s="4">
+        <v>0</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="4">
         <v>1</v>
@@ -1523,16 +1578,16 @@
         <v>1</v>
       </c>
       <c r="S8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" s="5">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>1</v>
-      </c>
-      <c r="V8" s="6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U8" s="5">
+        <v>1</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="W8" s="6">
         <v>1</v>
@@ -1547,19 +1602,19 @@
         <v>1</v>
       </c>
       <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="6">
         <v>0</v>
       </c>
       <c r="AD8" s="7">
         <v>1</v>
       </c>
       <c r="AE8" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="7">
         <v>1</v>
@@ -1568,20 +1623,26 @@
         <v>1</v>
       </c>
       <c r="AH8" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI8" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="AL8" s="2"/>
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
       <c r="AO8" s="2"/>
       <c r="AP8" s="2"/>
+      <c r="AQ8" s="2"/>
+      <c r="AR8" s="2"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -1600,11 +1661,11 @@
       <c r="F9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>16</v>
+      <c r="G9" s="4">
+        <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -1640,13 +1701,13 @@
         <v>1</v>
       </c>
       <c r="T9" s="5">
-        <v>1</v>
-      </c>
-      <c r="U9" s="6">
-        <v>1</v>
-      </c>
-      <c r="V9" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>1</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="W9" s="6">
         <v>1</v>
@@ -1661,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="AA9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="6">
+        <v>0</v>
       </c>
       <c r="AD9" s="7">
         <v>1</v>
@@ -1676,26 +1737,32 @@
         <v>0</v>
       </c>
       <c r="AF9" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9" s="7">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="AI9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="AL9" s="2"/>
       <c r="AM9" s="2"/>
       <c r="AN9" s="2"/>
       <c r="AO9" s="2"/>
       <c r="AP9" s="2"/>
+      <c r="AQ9" s="2"/>
+      <c r="AR9" s="2"/>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -1717,11 +1784,11 @@
       <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>16</v>
+      <c r="H10" s="4">
+        <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="4">
         <v>1</v>
@@ -1745,22 +1812,22 @@
         <v>1</v>
       </c>
       <c r="Q10" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="5">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
-        <v>1</v>
-      </c>
-      <c r="V10" s="6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U10" s="5">
+        <v>1</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="W10" s="6">
         <v>1</v>
@@ -1775,13 +1842,13 @@
         <v>1</v>
       </c>
       <c r="AA10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="6">
+        <v>0</v>
       </c>
       <c r="AD10" s="7">
         <v>1</v>
@@ -1793,23 +1860,29 @@
         <v>1</v>
       </c>
       <c r="AG10" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ10" s="2"/>
-      <c r="AK10" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="AL10" s="2"/>
       <c r="AM10" s="2"/>
       <c r="AN10" s="2"/>
       <c r="AO10" s="2"/>
       <c r="AP10" s="2"/>
+      <c r="AQ10" s="2"/>
+      <c r="AR10" s="2"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
@@ -1834,11 +1907,11 @@
       <c r="H11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>16</v>
+      <c r="I11" s="4">
+        <v>0</v>
       </c>
       <c r="J11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4">
         <v>1</v>
@@ -1868,13 +1941,13 @@
         <v>0</v>
       </c>
       <c r="T11" s="5">
-        <v>1</v>
-      </c>
-      <c r="U11" s="6">
-        <v>1</v>
-      </c>
-      <c r="V11" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>1</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="W11" s="6">
         <v>1</v>
@@ -1889,13 +1962,13 @@
         <v>1</v>
       </c>
       <c r="AA11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>0</v>
       </c>
       <c r="AD11" s="7">
         <v>1</v>
@@ -1904,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="AF11" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" s="7">
         <v>1</v>
@@ -1912,18 +1985,24 @@
       <c r="AH11" s="7">
         <v>1</v>
       </c>
-      <c r="AI11" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ11" s="2"/>
-      <c r="AK11" s="2"/>
+      <c r="AI11" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="8" t="s">
+        <v>30</v>
+      </c>
       <c r="AL11" s="2"/>
       <c r="AM11" s="2"/>
       <c r="AN11" s="2"/>
       <c r="AO11" s="2"/>
       <c r="AP11" s="2"/>
+      <c r="AQ11" s="2"/>
+      <c r="AR11" s="2"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
@@ -1951,11 +2030,11 @@
       <c r="I12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>16</v>
+      <c r="J12" s="4">
+        <v>0</v>
       </c>
       <c r="K12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="4">
         <v>1</v>
@@ -1979,37 +2058,37 @@
         <v>0</v>
       </c>
       <c r="S12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" s="5">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6">
-        <v>0</v>
-      </c>
-      <c r="V12" s="6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="5">
+        <v>1</v>
+      </c>
+      <c r="V12" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="W12" s="6">
         <v>1</v>
       </c>
       <c r="X12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AB12" s="6">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="6">
+        <v>0</v>
       </c>
       <c r="AD12" s="7">
         <v>1</v>
@@ -2026,18 +2105,24 @@
       <c r="AH12" s="7">
         <v>0</v>
       </c>
-      <c r="AI12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ12" s="2"/>
-      <c r="AK12" s="2"/>
+      <c r="AI12" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="8" t="s">
+        <v>31</v>
+      </c>
       <c r="AL12" s="2"/>
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
       <c r="AO12" s="2"/>
       <c r="AP12" s="2"/>
+      <c r="AQ12" s="2"/>
+      <c r="AR12" s="2"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
@@ -2068,11 +2153,11 @@
       <c r="J13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>16</v>
+      <c r="K13" s="4">
+        <v>0</v>
       </c>
       <c r="L13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="4">
         <v>1</v>
@@ -2096,22 +2181,22 @@
         <v>1</v>
       </c>
       <c r="T13" s="5">
-        <v>1</v>
-      </c>
-      <c r="U13" s="6">
-        <v>0</v>
-      </c>
-      <c r="V13" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>1</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="W13" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" s="6">
         <v>0</v>
@@ -2119,39 +2204,45 @@
       <c r="AA13" s="6">
         <v>0</v>
       </c>
-      <c r="AB13" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="7">
-        <v>1</v>
+      <c r="AB13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="6">
+        <v>0</v>
       </c>
       <c r="AD13" s="7">
         <v>1</v>
       </c>
       <c r="AE13" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="7">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ13" s="2"/>
-      <c r="AK13" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="AI13" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ13" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="8" t="s">
+        <v>32</v>
+      </c>
       <c r="AL13" s="2"/>
       <c r="AM13" s="2"/>
       <c r="AN13" s="2"/>
       <c r="AO13" s="2"/>
       <c r="AP13" s="2"/>
+      <c r="AQ13" s="2"/>
+      <c r="AR13" s="2"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -2185,11 +2276,11 @@
       <c r="K14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>16</v>
+      <c r="L14" s="4">
+        <v>0</v>
       </c>
       <c r="M14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="4">
         <v>1</v>
@@ -2204,28 +2295,28 @@
         <v>1</v>
       </c>
       <c r="R14" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="5">
-        <v>0</v>
-      </c>
-      <c r="U14" s="6">
-        <v>0</v>
-      </c>
-      <c r="V14" s="6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U14" s="5">
+        <v>1</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="W14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" s="6">
         <v>0</v>
@@ -2233,11 +2324,11 @@
       <c r="AA14" s="6">
         <v>0</v>
       </c>
-      <c r="AB14" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="7">
-        <v>1</v>
+      <c r="AB14" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="6">
+        <v>0</v>
       </c>
       <c r="AD14" s="7">
         <v>0</v>
@@ -2252,20 +2343,26 @@
         <v>0</v>
       </c>
       <c r="AH14" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ14" s="2"/>
-      <c r="AK14" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="7">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="AL14" s="2"/>
       <c r="AM14" s="2"/>
       <c r="AN14" s="2"/>
       <c r="AO14" s="2"/>
       <c r="AP14" s="2"/>
+      <c r="AQ14" s="2"/>
+      <c r="AR14" s="2"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
@@ -2302,11 +2399,11 @@
       <c r="L15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>16</v>
+      <c r="M15" s="4">
+        <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="4">
         <v>1</v>
@@ -2324,22 +2421,22 @@
         <v>0</v>
       </c>
       <c r="T15" s="5">
-        <v>1</v>
-      </c>
-      <c r="U15" s="6">
-        <v>0</v>
-      </c>
-      <c r="V15" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>1</v>
+      </c>
+      <c r="V15" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="W15" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" s="6">
         <v>0</v>
@@ -2347,11 +2444,11 @@
       <c r="AA15" s="6">
         <v>0</v>
       </c>
-      <c r="AB15" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="7">
-        <v>1</v>
+      <c r="AB15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="6">
+        <v>0</v>
       </c>
       <c r="AD15" s="7">
         <v>1</v>
@@ -2363,23 +2460,29 @@
         <v>0</v>
       </c>
       <c r="AG15" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="7">
         <v>1</v>
       </c>
-      <c r="AI15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ15" s="2"/>
-      <c r="AK15" s="2"/>
+      <c r="AI15" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK15" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="AL15" s="2"/>
       <c r="AM15" s="2"/>
       <c r="AN15" s="2"/>
       <c r="AO15" s="2"/>
       <c r="AP15" s="2"/>
+      <c r="AQ15" s="2"/>
+      <c r="AR15" s="2"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
@@ -2419,11 +2522,11 @@
       <c r="M16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="4" t="s">
-        <v>16</v>
+      <c r="N16" s="4">
+        <v>0</v>
       </c>
       <c r="O16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="4">
         <v>1</v>
@@ -2435,25 +2538,25 @@
         <v>1</v>
       </c>
       <c r="S16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" s="5">
-        <v>0</v>
-      </c>
-      <c r="U16" s="6">
-        <v>0</v>
-      </c>
-      <c r="V16" s="6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="U16" s="5">
+        <v>1</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="W16" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" s="6">
         <v>0</v>
@@ -2461,39 +2564,45 @@
       <c r="AA16" s="6">
         <v>0</v>
       </c>
-      <c r="AB16" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="7">
-        <v>1</v>
+      <c r="AB16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="6">
+        <v>0</v>
       </c>
       <c r="AD16" s="7">
         <v>1</v>
       </c>
       <c r="AE16" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" s="7">
         <v>1</v>
       </c>
       <c r="AH16" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ16" s="2"/>
-      <c r="AK16" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="7">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="AL16" s="2"/>
       <c r="AM16" s="2"/>
       <c r="AN16" s="2"/>
       <c r="AO16" s="2"/>
       <c r="AP16" s="2"/>
+      <c r="AQ16" s="2"/>
+      <c r="AR16" s="2"/>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -2536,11 +2645,11 @@
       <c r="N17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="O17" s="4" t="s">
-        <v>16</v>
+      <c r="O17" s="4">
+        <v>0</v>
       </c>
       <c r="P17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="5">
         <v>1</v>
@@ -2552,22 +2661,22 @@
         <v>1</v>
       </c>
       <c r="T17" s="5">
-        <v>1</v>
-      </c>
-      <c r="U17" s="6">
-        <v>0</v>
-      </c>
-      <c r="V17" s="6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>1</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="W17" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" s="6">
         <v>0</v>
@@ -2575,149 +2684,278 @@
       <c r="AA17" s="6">
         <v>0</v>
       </c>
-      <c r="AB17" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="7">
+      <c r="AB17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="6">
         <v>0</v>
       </c>
       <c r="AD17" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" s="7">
         <v>1</v>
       </c>
       <c r="AF17" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI17" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ17" s="2"/>
-      <c r="AK17" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK17" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="AL17" s="2"/>
       <c r="AM17" s="2"/>
       <c r="AN17" s="2"/>
       <c r="AO17" s="2"/>
       <c r="AP17" s="2"/>
+      <c r="AQ17" s="2"/>
+      <c r="AR17" s="2"/>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>1</v>
+      </c>
+      <c r="R18" s="5">
+        <v>1</v>
+      </c>
+      <c r="S18" s="5">
+        <v>1</v>
+      </c>
+      <c r="T18" s="5">
+        <v>1</v>
+      </c>
+      <c r="U18" s="5">
+        <v>1</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="W18" s="6">
+        <v>0</v>
+      </c>
+      <c r="X18" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="7">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL18" s="2"/>
+      <c r="AM18" s="2"/>
+      <c r="AN18" s="2"/>
+      <c r="AO18" s="2"/>
+      <c r="AP18" s="2"/>
+      <c r="AQ18" s="2"/>
+      <c r="AR18" s="2"/>
+    </row>
+    <row r="19" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="12" t="s">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="13" t="s">
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="W19" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="13"/>
-      <c r="AB18" s="14" t="s">
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="AC18" s="14"/>
-      <c r="AD18" s="14"/>
-      <c r="AE18" s="14"/>
-      <c r="AF18" s="14"/>
-      <c r="AG18" s="14"/>
-      <c r="AH18" s="14"/>
+      <c r="AE19" s="15"/>
+      <c r="AF19" s="15"/>
+      <c r="AG19" s="15"/>
+      <c r="AH19" s="15"/>
+      <c r="AI19" s="15"/>
+      <c r="AJ19" s="15"/>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="9"/>
-      <c r="AG20" s="9"/>
+    <row r="21" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="9"/>
+      <c r="AG21" s="9"/>
+      <c r="AH21" s="9"/>
+      <c r="AI21" s="9"/>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="10"/>
-      <c r="AF21" s="10"/>
-      <c r="AG21" s="10"/>
+    <row r="22" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1"/>
+      <c r="AG22" s="10"/>
+      <c r="AH22" s="10"/>
+      <c r="AI22" s="10"/>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="L22" s="1"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="10"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="10"/>
-      <c r="AF22" s="10"/>
-      <c r="AG22" s="10"/>
+    <row r="23" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="L23" s="1"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="10"/>
+      <c r="AF23" s="1"/>
+      <c r="AG23" s="10"/>
+      <c r="AH23" s="10"/>
+      <c r="AI23" s="10"/>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="L23" s="1"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="10"/>
-      <c r="AD23" s="1"/>
-      <c r="AE23" s="10"/>
-      <c r="AF23" s="10"/>
-      <c r="AG23" s="10"/>
+    <row r="24" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="L24" s="1"/>
+      <c r="AD24" s="9"/>
+      <c r="AE24" s="10"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="10"/>
+      <c r="AH24" s="10"/>
+      <c r="AI24" s="10"/>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="L24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="10"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="10"/>
-      <c r="AF24" s="10"/>
-      <c r="AG24" s="10"/>
+    <row r="25" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="L25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="10"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="10"/>
+      <c r="AH25" s="10"/>
+      <c r="AI25" s="10"/>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="L25" s="1"/>
-      <c r="AB25" s="9"/>
-      <c r="AC25" s="10"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
-      <c r="AG25" s="1"/>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="L26" s="1"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="10"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
+    <row r="27" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI17">
-    <sortCondition ref="AI2:AI17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AK18">
+    <sortCondition ref="AK3:AK18"/>
   </sortState>
   <mergeCells count="4">
-    <mergeCell ref="A18:P18"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="U18:AA18"/>
-    <mergeCell ref="AB18:AH18"/>
+    <mergeCell ref="A19:P19"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="W19:AC19"/>
+    <mergeCell ref="AD19:AJ19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
